--- a/daily_matches/job_matches_2026-07-01.xlsx
+++ b/daily_matches/job_matches_2026-07-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Internship, Machine Learning Engineer, Factory Software (Fall 2026)</t>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, OpenCV, Docker, Kubernetes, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,19 +496,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a24b26d7bdd47184</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f0aef032347c64</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Payment Optimization Data Scientist II</t>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,11 +517,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, XGBoost, CatBoost, BigQuery, Snowflake, Databricks, BigQuery, MySQL, Python</t>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c14d053975b72c</t>
+          <t>https://www.indeed.com/viewjob?jk=ccad7734d3de242e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Provisioning Engineer</t>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371ef99bbd6f0c8e</t>
+          <t>https://www.indeed.com/viewjob?jk=5da7530d86938f8a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>20</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f868b16fc5fbe2d</t>
+          <t>https://www.indeed.com/viewjob?jk=b60678a704bf64f4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Snowflake Streaming</t>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>20</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Kinesis, Snowflake, Databricks, BigQuery, Kafka, R, Java, Scala</t>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3062b19696d2ed9f</t>
+          <t>https://www.indeed.com/viewjob?jk=36eb953e60060a34</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, White Label Platform</t>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Upstart</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Git, Kafka, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11afa021c4ba1817</t>
+          <t>https://www.indeed.com/viewjob?jk=26cce728591c8fea</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, AKS, CI/CD, Python, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,42 +706,2737 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd1e469ef7af4497</t>
+          <t>https://www.indeed.com/viewjob?jk=d0b7f169148c17f4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Analytics Intern</t>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Snap Finance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>Princeton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>20</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4420962f77cb95c</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>20</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=73d0e018aa48bdbe</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>20</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=309c9cbc059c8ba5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e0124a9f6fa89c12</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>20</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3d66c118c15ff21</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>20</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=362bb4eb6549c026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>20</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0fa644ea1538f074</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Gilbert, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f5abf729578441a</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Hermitage, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>20</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76d12dad81a13d04</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Mechanicsburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>20</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc53707841ba936a</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>20</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2fc193932d24f51e</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>20</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a1081afe0268e25</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>20</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=618c638da5ec0631</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>20</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09b95de04181ac95</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>20</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=596f85db5b41871e</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>20</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f812b2c544d0156f</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>20</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd44e6a3d4a51495</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Lake Mary, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>20</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=70e9426795f88b93</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>20</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42e1bbbbceabf0a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>20</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92f7c36aeea5d079</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>20</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9bef5cb3ec873308</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>20</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b7a12a47cb0876b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>20</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=947c42dd2b306f7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Dayton, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>20</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ae39f02d0f294bea</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>20</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c142e3d444448160</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>20</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d74828eb28979387</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>20</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b039e5678ef59a9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Colorado Springs, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>20</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e2ac3d700e41e7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Jericho, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>20</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6919551aa68a5394</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>20</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ebb2824c263d220</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>20</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81f5345860f08559</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>20</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d80b7621b9e2f913</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>20</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c823870a08a1db65</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>20</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19d055e8ad0c2a80</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>20</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=382778aa87acaf4a</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>20</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=359dfc5821f41ea8</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>20</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ebd54d92f448b989</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>20</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=424df3bb9b87f31a</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>20</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a3eb31df717e0ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>20</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d29200f69d46c2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>20</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc844d8227e0c722</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>20</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e4c68521a1f351d</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>20</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f864b7c17caee013</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Davenport, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>20</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=736de4d3974ebb73</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Data &amp; ML Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>EssilorLuxottica</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Synapse, Data Lake, MLflow, Docker, Kubernetes, AKS, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f138b685e2cb7a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Data &amp; ML Engineer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>EssilorLuxottica</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Mason, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Synapse, Data Lake, MLflow, Docker, Kubernetes, AKS, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=231ded9c25f76bbd</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Cortex, Athena, Data Lake, Apache Airflow, Git, Snowflake</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=210c0c0b6772ab92</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Senior Data engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
           <t>TX, US USA</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D56" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Dataflow, Docker, Kubernetes, CI/CD, BigQuery, Kafka, MongoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=56ed3caee5240d78</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>WaFd Bank</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RAG, Cortex, Kinesis, CI/CD, Git, Snowflake, Kafka, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be6eb56bdb2b30c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Senior Data Architect</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>The Evolvers Group</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Git, Snowflake, PostgreSQL, MySQL, NoSQL, Python</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a80b58619ce00bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, AWS SageMaker, S3, EC2, Docker, Kubernetes, Terraform, Kafka</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=008ddae8bcb982b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>EssilorLuxottica</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Mason, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Synapse, Docker, Kubernetes, Git, Databricks</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c0b39b6a73a47a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Via Separations</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Watertown, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RAG, S3, FastAPI, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3e7b169aba6ca36</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Sr. AI Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Centurion Consulting Group</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, LLaMA, Mistral, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d5cb92a6b483e72c</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a8efa0e4c11321c</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Senior Engineer, Interactive Voice Response - AI/ML</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afeb152299c9c106</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Senior Engineer, Interactive Voice Response - AI/ML</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5533b8e5c44454a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Senior Engineer, Interactive Voice Response - AI/ML</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab4117b5e9d7c22d</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Senior Engineer, Interactive Voice Response - AI/ML</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=766f940fbd943625</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Terraform, PostgreSQL, MySQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f12357380affa13</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Generative AI Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, MLflow, Docker, Kubernetes, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f1f6b30db408e92</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Synctera</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Kubernetes, Terraform, Git, Snowflake, BigQuery, PostgreSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ff068a853e2e8ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Synctera</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Kubernetes, Terraform, Git, Snowflake, BigQuery, PostgreSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ce8466bc8f4ae9d</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>RePurpose Global</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=462bc9e89d44b0ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Conversational AI</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Asurion</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Kafka, MongoDB, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4819c0a20b1980c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior Research Engineer, Computer Vision (LFV/WFM)</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Toyota Research Institute</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Los Altos, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, PyTorch, AWS SageMaker, EC2, Docker, Kubernetes, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94e05c220fd5f46f</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Java/Full-stack Engineer - Security Engineer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Truist</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83272652072888d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>C-4 Analytics</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Wakefield, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Snowflake, MongoDB, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84c8995ff51aec7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Womble Bond Dickinson</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, Synapse, Dataflow, Git, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac8fb71cef7c6797</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Menlo Park, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
         <v>10</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Prompt Engineering, Tableau, Power BI, Python, SQL, R, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4675a825d27ca334</t>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Redshift, BigQuery, CI/CD, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87118ad523a8dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Senior Business Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>WilmerHale</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, PySpark, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3766eea758ba5c91</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer 1</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>WEX Inc.</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Portland, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f5e1d20485e6d34c</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>AWS Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>RAG, S3, Glue, Git, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7ef214e1d2011be</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>AI Solutions Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Data Lake, CI/CD, Git, Snowflake, Databricks, R, Scala</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=36ee3dc60df682d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Santa Monica, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, GitHub Actions, Terraform, Git, Kafka, PostgreSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=32b4003243d1b08e</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer/Architect</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>West Monroe</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Snowflake, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b2a2f474f9f2e859</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Software Engineer II - JavaScript - Enterprise Architecture</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Jenkins, Cassandra, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf754e597f6f864c</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Intern-AI Automation &amp; Process Analyst</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>CPI Card Group</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Littleton, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09ad2bdb1d00b774</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-01.xlsx
+++ b/daily_matches/job_matches_2026-07-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,122 +468,122 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, MarTech</t>
+          <t>Senior Product Software Engineer - Linear Advertising Platform</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Bristol, CT, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.6</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, TensorFlow, PyTorch, AWS SageMaker</t>
+          <t>Data Scientist, RAG, Copilot, Kinesis, Docker, Kubernetes, Terraform, Git, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0a8b4ddc2c212a6</t>
+          <t>https://www.indeed.com/viewjob?jk=59abce8159d1399a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI/Data Science Engineer II</t>
+          <t>Senior SDET</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Git, Snowflake, Databricks, BigQuery, Redshift</t>
+          <t>S3, EC2, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa4914e8c40e18d9</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0c1dbb6abf6b0e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI</t>
+          <t>Senior SDET</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, Apache Airflow, CI/CD</t>
+          <t>S3, EC2, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f069643153aaaa93</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac5da3fd48d3bd5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. AI Architect</t>
+          <t>AI Full Stack Engineer – Client Engineering Team</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>I2E Consulting Pvt Ltd</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Prompt Engineering, BigQuery, Dataflow, MLflow, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, Copilot, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c30f9895c7415caa</t>
+          <t>https://www.indeed.com/viewjob?jk=85027552c9144bdc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Foundational Model Engineer</t>
+          <t>Machine Learning and Generative AI Engineer, Digital Transformation</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Harvard University</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,252 +626,252 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, MLflow, Kubernetes, CI/CD, Git</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Pinecone, TensorFlow, PyTorch, CI/CD, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d203e674e61ddd8c</t>
+          <t>https://www.indeed.com/viewjob?jk=3d6a7d968090de37</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Solutions Software Developer</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AtkinsRéalis</t>
+          <t>Meijer</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, PyTorch, Keras, Data Lake, CI/CD, Git, Databricks, Tableau</t>
+          <t>Data Scientist, TensorFlow, PyTorch, NLTK, Azure ML, Synapse, Git, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6623209a0f6f745a</t>
+          <t>https://www.indeed.com/viewjob?jk=c03743c555ed5d5e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Credit Union of Texas</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Hugging Face, Prompt Engineering, S3, Docker, Kafka, Hadoop, MongoDB, Cassandra</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Python, SQL, R, Scala, Optimization, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=712497bf338832f5</t>
+          <t>https://www.indeed.com/viewjob?jk=0c7ddb04b6a6fe7a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer AI/ML Ops</t>
+          <t>Senior Data Science Analyst</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>Harver</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LangChain, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, Apache Airflow, CI/CD, PySpark, Python</t>
+          <t>Data Scientist, XGBoost, Git, Tableau, Power BI, Python, SQL, R, Scala, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817383301a886adf</t>
+          <t>https://www.indeed.com/viewjob?jk=5b329b9c90b37fd9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Cyber Artificial Intelligence Operations Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Edgewater Federal Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, LLaMA, Mistral, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform</t>
+          <t>BigQuery, CI/CD, BigQuery, PostgreSQL, MongoDB, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bbd4c8495cb1568</t>
+          <t>https://www.indeed.com/viewjob?jk=bf3f3aa00aab5da7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Azure Databricks Admin</t>
+          <t>Software Engineer - Professional Archive Search</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Smarsh</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, GitHub Actions, Git, Databricks, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30458fe3d780cd5e</t>
+          <t>https://www.indeed.com/viewjob?jk=e60e2803ad752d0e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Financial Data Engineer</t>
+          <t>Senior SOCD Applied AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Jenkins, BigQuery, Tableau, Python, SQL, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, FastAPI, CI/CD, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56390aee6504595</t>
+          <t>https://www.indeed.com/viewjob?jk=12e7d30d39a44b18</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Platform Engineering &amp; Developer (Devops)</t>
+          <t>Data Strategist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Greenville-Spartanburg Airport District</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Greer, SC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>RAG, Redshift, Synapse, Data Lake, Snowflake, Redshift, Power BI, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,322 +881,77 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f580e1e472b5dd8</t>
+          <t>https://www.indeed.com/viewjob?jk=aca3044738ad4c13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. AI Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Grace Hill</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, BigQuery, Dataflow, Docker, Terraform, BigQuery, Python, SQL, R</t>
+          <t>RAG, Git, MySQL, MongoDB, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e61e632ba68e42b</t>
+          <t>https://www.indeed.com/viewjob?jk=e5cf63e840ff0cc6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Prompt Engineer</t>
+          <t>Media Streaming Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Copilot, AKS, Git, R, Scala, Optimization, A/B Testing</t>
+          <t>Data Scientist, Generative AI, RAG, EC2, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a0efc4bbc3f179d</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Data Analyst / Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>McAfee</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Frisco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, Databricks, Kafka, PostgreSQL, MongoDB, NoSQL, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bff5e93f15d9f562</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Healthcare Provider AI Decision Science Consultant</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Logic, Inc.</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8c675fe56d63abfa</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Sr Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Workday</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, Git, Kafka, Python, R</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=878fd418f598501c</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Data Analyst - Digital &amp; E-commerce (experimentation, ML, Math/Stats)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Hadoop, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=66eea046e3fcd77d</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Carnegie Mellon University</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, FastAPI, AKS, CI/CD, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf337ea24ca6233</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Aviation Programmer Analyst</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Textron Airborne Solutions</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Git, PostgreSQL, Tableau, Matplotlib, Seaborn, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3dee8423f45d2aa3</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Aviation Programmer Analyst</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Textron Airborne Solutions</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Git, PostgreSQL, Tableau, Matplotlib, Seaborn, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ee55e10fd42a5958</t>
+          <t>https://www.indeed.com/viewjob?jk=5146dde060a8b8c8</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-01.xlsx
+++ b/daily_matches/job_matches_2026-07-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Product Software Engineer - Linear Advertising Platform</t>
+          <t>Sr Data Science Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LegitScript</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bristol, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Kinesis, Docker, Kubernetes, Terraform, Git, Kafka, MySQL</t>
+          <t>Generative AI, RAG, Prompt Engineering, MLflow, Docker, Apache Airflow, CI/CD, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59abce8159d1399a</t>
+          <t>https://www.indeed.com/viewjob?jk=580347ece6eeeb68</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior SDET</t>
+          <t>Artificial Intelligence - AI Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Pellera Technologies</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>S3, EC2, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad0c1dbb6abf6b0e</t>
+          <t>https://www.indeed.com/viewjob?jk=205b4542690526b4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior SDET</t>
+          <t>Artificial Intelligence - AI Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Pellera Technologies</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>S3, EC2, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac5da3fd48d3bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=e73a06d83fe38775</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Full Stack Engineer – Client Engineering Team</t>
+          <t>Data Engineer, Training Transformation</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>I2E Consulting Pvt Ltd</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, Git, NoSQL, Python</t>
+          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Kafka, Hadoop, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85027552c9144bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=d2acffa5291128c4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Machine Learning and Generative AI Engineer, Digital Transformation</t>
+          <t>Senior Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Harvard University</t>
+          <t>RectorSeal</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Pinecone, TensorFlow, PyTorch, CI/CD, Git</t>
+          <t>RAG, Azure ML, Synapse, Data Lake, CI/CD, GitHub Actions, Git, Databricks, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d6a7d968090de37</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a61d914fd12568</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Software Engineer Sr (Java)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Meijer</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, NLTK, Azure ML, Synapse, Git, Databricks, PySpark, Python</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c03743c555ed5d5e</t>
+          <t>https://www.indeed.com/viewjob?jk=d6c1b0c25c4f79fb</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Credit Union of Texas</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Python, SQL, R, Scala, Optimization, Hypothesis Testing</t>
+          <t>Data Scientist, RAG, Copilot, Docker, Kubernetes, Jenkins, GitHub Actions, Terraform, Git, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c7ddb04b6a6fe7a</t>
+          <t>https://www.indeed.com/viewjob?jk=bd85dafda269f4cd</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Science Analyst</t>
+          <t>Data/Analytics Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Harver</t>
+          <t>Heluna Health</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, XGBoost, Git, Tableau, Power BI, Python, SQL, R, Scala, Hypothesis Testing</t>
+          <t>Data Scientist, CI/CD, GitHub Actions, Terraform, Git, Databricks, PySpark, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b329b9c90b37fd9</t>
+          <t>https://www.indeed.com/viewjob?jk=2c0b7cd5c47cd65a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BigQuery, CI/CD, BigQuery, PostgreSQL, MongoDB, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf3f3aa00aab5da7</t>
+          <t>https://www.indeed.com/viewjob?jk=cd1988f00e94a6dc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer - Professional Archive Search</t>
+          <t>Senior AI App Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Smarsh</t>
+          <t>Precision CastParts</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Clackamas, OR, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Redshift, CI/CD, Git, Snowflake, Databricks, Redshift, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e60e2803ad752d0e</t>
+          <t>https://www.indeed.com/viewjob?jk=5197a4f7fe1f8f98</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior SOCD Applied AI Engineer</t>
+          <t>Senior Application System Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, FastAPI, CI/CD, Python, R</t>
+          <t>RAG, Copilot, BigQuery, CI/CD, Git, BigQuery, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12e7d30d39a44b18</t>
+          <t>https://www.indeed.com/viewjob?jk=1d25899ee1f9c7e2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Strategist</t>
+          <t>Sr Software Engineer II - GCP, Java/Python - The Personalization, Brand, and Communications Technology</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Greenville-Spartanburg Airport District</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Greer, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Synapse, Data Lake, Snowflake, Redshift, Power BI, R, Scala</t>
+          <t>RAG, Copilot, BigQuery, Dataflow, CI/CD, Git, BigQuery, Python, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aca3044738ad4c13</t>
+          <t>https://www.indeed.com/viewjob?jk=a59fa4d633d31656</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Sr Software Engineer II - GCP, Java/Python - The Personalization, Brand, and Communications Technology</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Versant</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Git, MySQL, MongoDB, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, BigQuery, Dataflow, CI/CD, Git, BigQuery, Python, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,42 +916,1932 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5cf63e840ff0cc6</t>
+          <t>https://www.indeed.com/viewjob?jk=ec8b3b2a7eb7da37</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Media Streaming Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Datavault AI</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9677be782841e9b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>GraphRAG Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Illumination Works llc</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, PyTorch, spaCy, Git, Python</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d7df07bca84c727</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>McKesson</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Generative AI, Redshift, Data Lake, CI/CD, Git, Databricks, Redshift, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=17aa6109dc953b4d</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Revenue Analytics</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, Athena, Redshift, Data Lake, Redshift, PostgreSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=20816e56499c7f07</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Curriculum Associates</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, S3, Data Lake, Kafka, Hadoop, MySQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f46ca1a397036c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Bharathvio Technologies</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Kent, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Git, BigQuery, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a669b5372e08d533</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Platform Engineering &amp; Developer (Devops)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0c291ee6cbc4d62</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MHK TECH</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Lake, Kubernetes, CI/CD, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb4348c2e52b6813</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=79feb687bb72ac78</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=adce1a621858f3c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2efcb6241262a6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5537c394ba928d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d3c8af179bc0778</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Oklahoma City, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba73192b84e9a014</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Albany, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f3f2c208c49ad2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd503fb31373cea4</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=384dad477a7d4c37</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91dc5ef2fe68eb7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81230b7c434670b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc645ae222db3e10</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d7036a52751036a</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1d04bcde8eba209</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2502e94f51a49b51</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19e2cfcaf144075d</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=95e0e04a74b1ff94</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4360cb8882d4607c</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a6c0949bccb6bb0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f77798d099cb8b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Bentonville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2be707d0231f4f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52f343557c37913b</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f6572f21e3ba82b</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Saint Petersburg, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68041bd56620fc23</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Scottsdale, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50ccf8e994e2f3e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00f786347a83e3c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Walnut Creek, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=586d92851e07e198</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f15ae99ec730529</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f1ba093fa8b8a19</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b3b85a9a4229e8a</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Carmel, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dbe65860bcbe894a</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Culver City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=219d6fb2b9a5277a</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=02f7aad5e123275d</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d54af4303e7a87f</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Overland Park, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=41d4fc5d0a360384</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee2c234247571ed2</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Healthcare Provider AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a92030606e8244de</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Visiting Research Data Scientist - Illinois Fire Service Institute</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>University of Illinois</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Urbana, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aee944aea4e3bc70</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Reyes Holdings</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Rosemont, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, Azure ML, MLflow, Snowflake, Databricks, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=022066fbc1a4c4e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>QA Automation Engineer I</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Hy-Vee, Inc.</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>West Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
         <v>10</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, EC2, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5146dde060a8b8c8</t>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dccc90c8e154807a</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Bioinformatics Data Scientist</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>L3harries</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b847321fff66bb3</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Technical AIP Data Analyst</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Altenar</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Malta, MT, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RAG, Git, Hadoop, NoSQL, Tableau, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2cb0b445fe558270</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Data Engineer - Big Data Platform</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>PNC Financial Services Group</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Apache Airflow, Hadoop, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=405d8c4a6a09373a</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Data Science Senior Associate - Consumer Bank Marketing Analytics</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Git, Tableau, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb2bc00ba8ebe964</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Analytics &amp; AI Intern</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>AmWINS Group, Inc</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Windsor, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, Power BI, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=649dffa4a815314c</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Data Scientist (On-Site in Boston, MA)</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Genentech</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Data Scientist, XGBoost, MLflow, Docker, Git, Python, R, Scala, Bayesian</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c0e9d3e2caa90a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>AI Native Technical Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>JD.com</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, CI/CD, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0677cc8186999a52</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-01.xlsx
+++ b/daily_matches/job_matches_2026-07-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Applied AI Product Engineer (Remote Opportunity)</t>
+          <t>AI Specialist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>Kenneth Copeland Ministries</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Newark, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b78491aad625680</t>
+          <t>https://www.indeed.com/viewjob?jk=5ce92c0fbadcfe0f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Applied AI Product Engineer (Remote Opportunity)</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
+          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Terraform, Git, Snowflake, Databricks, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14434f26fcf074be</t>
+          <t>https://www.indeed.com/viewjob?jk=edba7e9ad21f7227</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Machine Learning and Generative AI Engineer, Digital Transformation</t>
+          <t>Senior Full-Stack AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Harvard University</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Pinecone, TensorFlow, PyTorch, CI/CD, Git</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Python, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1922c5bacd22cda3</t>
+          <t>https://www.indeed.com/viewjob?jk=9943ae9f36831f9c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Solutions Engineer</t>
+          <t>Data Solutions Architect (Financial Services)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Heaven Hill</t>
+          <t>SunnyData</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, LLaMA, Gemini, Copilot, CI/CD, Git, Power BI, Python</t>
+          <t>RAG, S3, Databricks, Kafka, Hadoop, Cassandra, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83526d2abec8f288</t>
+          <t>https://www.indeed.com/viewjob?jk=b839de2e42fa796c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior AI Software Developer</t>
+          <t>Mid- Level Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pyramid Systems Inc</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, MLflow, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git</t>
+          <t>RAG, Synapse, Data Lake, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a84346c1964ec20</t>
+          <t>https://www.indeed.com/viewjob?jk=03dd8c61c6f7c9a3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Developer</t>
+          <t>Cyber Security Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Weris, Inc.</t>
+          <t>Bectran Inc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Middletown, PA, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb89f2f1797cfb24</t>
+          <t>https://www.indeed.com/viewjob?jk=d55d6bf14862ee19</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Full Stack python Developer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DataSys America</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Docker, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6155921d8ae1c685</t>
+          <t>https://www.indeed.com/viewjob?jk=27c62c4e7ce52816</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Full-Stack Java Architect with Co-Pilot Experience</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Intellibus</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcfa249c1b1aaead</t>
+          <t>https://www.indeed.com/viewjob?jk=c26df8ecfe6a67d7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Delta Dental</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, BigQuery, CI/CD, Terraform, Git, BigQuery, Python, SQL</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63ca6ceabfc0470d</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c27c0e013e3176</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (contract)</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, Gemini, Pinecone, Prompt Engineering, Docker, Kubernetes, Git, Python, R</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61cc014a72a1abd1</t>
+          <t>https://www.indeed.com/viewjob?jk=77c6fc067a14cd01</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Full Stack Developer: Ai Enablement and Agentic Develoopment</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Excellis Consulting Corporation</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9aedd178e13717</t>
+          <t>https://www.indeed.com/viewjob?jk=36ae43139e421015</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Autonomous Driving Senior Vehicle Perception Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Northville, MI, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, OpenCV, YOLO, Git, Python, R, Optimization</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d52eb904e714339</t>
+          <t>https://www.indeed.com/viewjob?jk=658083105be37fc9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Public Health Solutions (NYC)</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, FastAPI, Docker, Databricks, Python, SQL, R</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68597fe6aa1d1435</t>
+          <t>https://www.indeed.com/viewjob?jk=37b5b6c3a2a9b089</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Meijer</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, Copilot, TensorFlow, PyTorch, Azure ML, Synapse, Databricks, PySpark, Python, SQL</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b1db4bd7c23ce37</t>
+          <t>https://www.indeed.com/viewjob?jk=ff874c726c6d174b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Docker, Kubernetes, GitHub Actions, Git, Kafka, Python, SQL, R</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0f4cd7071264d74</t>
+          <t>https://www.indeed.com/viewjob?jk=be5f2c43370385dc</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Full Stack Application Developer II</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SMS group GmbH</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf3af53dcc9e2f3f</t>
+          <t>https://www.indeed.com/viewjob?jk=d146448bc1ed6f8a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Long Key, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Docker, CI/CD, GitHub Actions, Git, Snowflake, Python, R, Scala</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0ed8fc69de419e8</t>
+          <t>https://www.indeed.com/viewjob?jk=1ba0ba045d78e688</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Revelation Pharma</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Prompt Engineering, S3, MLflow, R, Scala, Optimization, Bayesian, A/B Testing</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d09c3a75fde8fd4</t>
+          <t>https://www.indeed.com/viewjob?jk=96dc41f3d1e6ef0d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Joby Aviation</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Carlos, CA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Git, Kafka, PostgreSQL, MongoDB, Python, SQL, R</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84e616417529d237</t>
+          <t>https://www.indeed.com/viewjob?jk=e4bae38df86e03d8</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineering LMTS</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Middletown, DE, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Generative AI, Copilot, Prompt Engineering, Git, Tableau, Python, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=086342fe399dbfbe</t>
+          <t>https://www.indeed.com/viewjob?jk=50a180a1e1ed21cb</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Technical Architect, Dairy Predictive Solutions</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Corrales, NM, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, CI/CD, Databricks, Python, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33652e6c92967b96</t>
+          <t>https://www.indeed.com/viewjob?jk=808ddd7c43b55f71</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Snowflake, PostgreSQL, Power BI, SQL, R, Scala</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=327bd43487b4864b</t>
+          <t>https://www.indeed.com/viewjob?jk=42460f2d5d6c2dc2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CERTIFID</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>BigQuery, Docker, Kubernetes, CI/CD, BigQuery, Tableau, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2ea249ca23dcb7b</t>
+          <t>https://www.indeed.com/viewjob?jk=cad8c4f4c77ffbb5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CERTIFID</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>BigQuery, Docker, Kubernetes, CI/CD, BigQuery, Tableau, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a78d1198797715b3</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8d0a5e82c1874b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. AI Platform Developer (Remote in U.S.)</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>U.S. Green Building Council</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, S3, Git, Snowflake, Power BI, Python, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98c0ed4c878506aa</t>
+          <t>https://www.indeed.com/viewjob?jk=0e6a850caef1d56c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Junior Data Scientist</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Applied Research Associates, Inc</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Hot Springs Village, AR, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Data Scientist, PyTorch, Git, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d03a4a80fc4f0323</t>
+          <t>https://www.indeed.com/viewjob?jk=e8123be1cb7ab6fe</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer IV</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Trinity Health</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Copilot, CI/CD, Git, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e40726f171c1360c</t>
+          <t>https://www.indeed.com/viewjob?jk=7b64294d24071838</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,42 +1441,1302 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c64b187a3d8a0ecb</t>
+          <t>https://www.indeed.com/viewjob?jk=7204e97c970316ba</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I - Finance</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d2fa88614b071867</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0ffda87ddfb642b</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=047558f0baabe95a</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Jackson, MS, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e9c9a818bf8a86c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Hope Hull, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c7cc5edd8948ce9</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Kennesaw, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f38bf854652c94f</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be842fb79d8cc443</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Fremont, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5fd2a43ada3bc92</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Pawtucket, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ce1ae8e7b69f496</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>New Franken, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d885cd296a96b39</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1f2f9e0c1ec3263</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>UT, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c7e382d6d5ade69</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a054f6247f0af463</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Columbia, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d67e69c8f22631f</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Okemos, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=edc29795b2e72de2</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Baton Rouge, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15b875d534cd3ea2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d1f71919ce639a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Charleston, WV, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b39116b0df22731</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Walnut Creek, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=011066a877bea2b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fdf9ba4924c8cbfe</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Upper Darby, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e8da43a2a43902c</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=23eb72012db7f8d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b9c983a104094bc3</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>TN, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ac0b7f78a02869c</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=887cb24b5bd4709d</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Forward Financing</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RAG, Cortex, Redshift, Snowflake, Redshift, Kafka, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97ebbb0917e752e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Forward Financing</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ontario, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RAG, Cortex, Redshift, Snowflake, Redshift, Kafka, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d7723e13251c2868</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Equiniti</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Woburn, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a43443df5ed27936</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Sr. AI Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Hugging Face, PyTorch, CI/CD, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d71c3cb7ab15def</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Snowflake, Databricks, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=675e69b0715a24da</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Senior Associate Software &amp; Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>LSEG (London Stock Exchange Group)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5d27da61496d978</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Senior Data scientist</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68dca612a39f8fd3</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Subway</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
         <v>10</v>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, FastAPI, Docker, CI/CD, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a358260b326ed5</t>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=621a2f404ef769bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Subway</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Shelton, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=766ac874b2ab78b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Forward Deployment Engineer (FDE / Java Full Stack + GenAI)</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, CI/CD, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5fc82c9ba18105e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Software Engineer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Charles Schwab</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Southlake, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Copilot, S3, CI/CD, Git, PostgreSQL, SQL, R, Java, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4671e60dd2cd92a</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - API &amp; MCP Platform</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>ZoomInfo</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Kafka, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e761fb98aee2a94</t>
         </is>
       </c>
     </row>
